--- a/特価商品.xlsx
+++ b/特価商品.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codex用カタログ元データ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanei004\Documents\GitHub\sanei-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B14135-A2E8-4C96-8961-3E555A759F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98B1A1D-90F6-4135-B71B-B374A412BDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="375" windowWidth="25125" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="495" windowWidth="28485" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="特価商品" sheetId="1" r:id="rId1"/>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2">
         <v>40</v>

--- a/特価商品.xlsx
+++ b/特価商品.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanei004\Documents\GitHub\sanei-catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98B1A1D-90F6-4135-B71B-B374A412BDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC30E96-1EF3-4418-97C4-F2376143B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="495" windowWidth="28485" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29115" yWindow="285" windowWidth="28485" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="特価商品" sheetId="1" r:id="rId1"/>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
         <v>10</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2">
         <v>20</v>
@@ -1061,7 +1061,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2">
         <v>30</v>
